--- a/artfynd/A 59375-2024 artfynd.xlsx
+++ b/artfynd/A 59375-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121417502</v>
+        <v>121417437</v>
       </c>
       <c r="B5" t="n">
-        <v>91995</v>
+        <v>91996</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481952</v>
+        <v>482034</v>
       </c>
       <c r="R5" t="n">
-        <v>6853594</v>
+        <v>6853593</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121417437</v>
+        <v>121419373</v>
       </c>
       <c r="B6" t="n">
-        <v>91995</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,25 +1122,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482034</v>
+        <v>481995</v>
       </c>
       <c r="R6" t="n">
-        <v>6853593</v>
+        <v>6853657</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121419373</v>
+        <v>121417584</v>
       </c>
       <c r="B7" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,13 +1252,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481995</v>
+        <v>481916</v>
       </c>
       <c r="R7" t="n">
-        <v>6853657</v>
+        <v>6853628</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1302,12 +1302,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1317,7 +1317,7 @@
         <v>121419297</v>
       </c>
       <c r="B8" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121417584</v>
+        <v>121417502</v>
       </c>
       <c r="B9" t="n">
-        <v>98104</v>
+        <v>91996</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1428,25 +1428,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481916</v>
+        <v>481952</v>
       </c>
       <c r="R9" t="n">
-        <v>6853628</v>
+        <v>6853594</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1506,12 +1506,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 59375-2024 artfynd.xlsx
+++ b/artfynd/A 59375-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121417437</v>
+        <v>121419297</v>
       </c>
       <c r="B5" t="n">
-        <v>91996</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482034</v>
+        <v>481958</v>
       </c>
       <c r="R5" t="n">
-        <v>6853593</v>
+        <v>6853670</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1098,22 +1098,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121419373</v>
+        <v>121417502</v>
       </c>
       <c r="B6" t="n">
-        <v>98105</v>
+        <v>91996</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,25 +1122,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481995</v>
+        <v>481952</v>
       </c>
       <c r="R6" t="n">
-        <v>6853657</v>
+        <v>6853594</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1314,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121419297</v>
+        <v>121419373</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1326,25 +1326,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,13 +1354,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481958</v>
+        <v>481995</v>
       </c>
       <c r="R8" t="n">
-        <v>6853670</v>
+        <v>6853657</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1404,19 +1404,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121417502</v>
+        <v>121417437</v>
       </c>
       <c r="B9" t="n">
         <v>91996</v>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481952</v>
+        <v>482034</v>
       </c>
       <c r="R9" t="n">
-        <v>6853594</v>
+        <v>6853593</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 59375-2024 artfynd.xlsx
+++ b/artfynd/A 59375-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121419297</v>
+        <v>121419373</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481958</v>
+        <v>481995</v>
       </c>
       <c r="R5" t="n">
-        <v>6853670</v>
+        <v>6853657</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,12 +1098,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121417584</v>
+        <v>121417437</v>
       </c>
       <c r="B7" t="n">
-        <v>98105</v>
+        <v>91996</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,25 +1224,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481916</v>
+        <v>482034</v>
       </c>
       <c r="R7" t="n">
-        <v>6853628</v>
+        <v>6853593</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1302,22 +1302,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121419373</v>
+        <v>121419297</v>
       </c>
       <c r="B8" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1326,25 +1326,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,13 +1354,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481995</v>
+        <v>481958</v>
       </c>
       <c r="R8" t="n">
-        <v>6853657</v>
+        <v>6853670</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1404,22 +1404,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121417437</v>
+        <v>121417584</v>
       </c>
       <c r="B9" t="n">
-        <v>91996</v>
+        <v>98105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1428,25 +1428,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482034</v>
+        <v>481916</v>
       </c>
       <c r="R9" t="n">
-        <v>6853593</v>
+        <v>6853628</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1506,12 +1506,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 59375-2024 artfynd.xlsx
+++ b/artfynd/A 59375-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121419373</v>
+        <v>121417502</v>
       </c>
       <c r="B5" t="n">
-        <v>98105</v>
+        <v>91996</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481995</v>
+        <v>481952</v>
       </c>
       <c r="R5" t="n">
-        <v>6853657</v>
+        <v>6853594</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121417502</v>
+        <v>121419297</v>
       </c>
       <c r="B6" t="n">
-        <v>91996</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,25 +1122,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481952</v>
+        <v>481958</v>
       </c>
       <c r="R6" t="n">
-        <v>6853594</v>
+        <v>6853670</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1200,22 +1200,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121417437</v>
+        <v>121419373</v>
       </c>
       <c r="B7" t="n">
-        <v>91996</v>
+        <v>98105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,25 +1224,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1252,13 +1252,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482034</v>
+        <v>481995</v>
       </c>
       <c r="R7" t="n">
-        <v>6853593</v>
+        <v>6853657</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121419297</v>
+        <v>121417437</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>91996</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1326,25 +1326,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481958</v>
+        <v>482034</v>
       </c>
       <c r="R8" t="n">
-        <v>6853670</v>
+        <v>6853593</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1404,12 +1404,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 59375-2024 artfynd.xlsx
+++ b/artfynd/A 59375-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121417502</v>
+        <v>121419297</v>
       </c>
       <c r="B5" t="n">
-        <v>91996</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481952</v>
+        <v>481958</v>
       </c>
       <c r="R5" t="n">
-        <v>6853594</v>
+        <v>6853670</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1098,22 +1098,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121419297</v>
+        <v>121419373</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,25 +1122,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481958</v>
+        <v>481995</v>
       </c>
       <c r="R6" t="n">
-        <v>6853670</v>
+        <v>6853657</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,22 +1200,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121419373</v>
+        <v>121417437</v>
       </c>
       <c r="B7" t="n">
-        <v>98105</v>
+        <v>92004</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,25 +1224,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1252,13 +1252,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481995</v>
+        <v>482034</v>
       </c>
       <c r="R7" t="n">
-        <v>6853657</v>
+        <v>6853593</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121417437</v>
+        <v>121417502</v>
       </c>
       <c r="B8" t="n">
-        <v>91996</v>
+        <v>92004</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482034</v>
+        <v>481952</v>
       </c>
       <c r="R8" t="n">
-        <v>6853593</v>
+        <v>6853594</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1419,7 +1419,7 @@
         <v>121417584</v>
       </c>
       <c r="B9" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 59375-2024 artfynd.xlsx
+++ b/artfynd/A 59375-2024 artfynd.xlsx
@@ -1110,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121419373</v>
+        <v>121417437</v>
       </c>
       <c r="B6" t="n">
-        <v>98113</v>
+        <v>92004</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,25 +1122,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481995</v>
+        <v>482034</v>
       </c>
       <c r="R6" t="n">
-        <v>6853657</v>
+        <v>6853593</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121417437</v>
+        <v>121419373</v>
       </c>
       <c r="B7" t="n">
-        <v>92004</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,25 +1224,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1252,13 +1252,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482034</v>
+        <v>481995</v>
       </c>
       <c r="R7" t="n">
-        <v>6853593</v>
+        <v>6853657</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 59375-2024 artfynd.xlsx
+++ b/artfynd/A 59375-2024 artfynd.xlsx
@@ -1110,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121417437</v>
+        <v>121419373</v>
       </c>
       <c r="B6" t="n">
-        <v>92004</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,25 +1122,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482034</v>
+        <v>481995</v>
       </c>
       <c r="R6" t="n">
-        <v>6853593</v>
+        <v>6853657</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121419373</v>
+        <v>121417437</v>
       </c>
       <c r="B7" t="n">
-        <v>98113</v>
+        <v>92004</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,25 +1224,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1252,13 +1252,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481995</v>
+        <v>482034</v>
       </c>
       <c r="R7" t="n">
-        <v>6853657</v>
+        <v>6853593</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
